--- a/src-tauri/samples/mame/16_mame_agilent_numeric_confirmation.xlsx
+++ b/src-tauri/samples/mame/16_mame_agilent_numeric_confirmation.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B95"/>
+  <dimension ref="A1:B85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -586,7 +586,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1487.3</v>
+        <v>2373.9</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1487.3</v>
+        <v>2373.9</v>
       </c>
     </row>
     <row r="20">
@@ -634,7 +634,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1507</v>
+        <v>2344.3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1507</v>
+        <v>2344.3</v>
       </c>
     </row>
     <row r="25">
@@ -682,7 +682,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1034.2</v>
+        <v>1832.1</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1034.2</v>
+        <v>1832.1</v>
       </c>
     </row>
     <row r="30">
@@ -730,7 +730,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1004.7</v>
+        <v>1802.6</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1004.7</v>
+        <v>1802.6</v>
       </c>
     </row>
     <row r="35">
@@ -778,7 +778,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1812.4</v>
+        <v>3073.2</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1812.4</v>
+        <v>3073.2</v>
       </c>
     </row>
     <row r="40">
@@ -826,7 +826,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1842</v>
+        <v>3023.9</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1842</v>
+        <v>3023.9</v>
       </c>
     </row>
     <row r="45">
@@ -874,7 +874,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1605.5</v>
+        <v>1516.9</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1605.5</v>
+        <v>1516.9</v>
       </c>
     </row>
     <row r="50">
@@ -922,7 +922,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1576</v>
+        <v>1487.3</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1576</v>
+        <v>1487.3</v>
       </c>
     </row>
     <row r="55">
@@ -970,7 +970,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>3063.3</v>
+        <v>1172.1</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3063.3</v>
+        <v>1172.1</v>
       </c>
     </row>
     <row r="60">
@@ -1018,7 +1018,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>3023.9</v>
+        <v>1142.6</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3023.9</v>
+        <v>1142.6</v>
       </c>
     </row>
     <row r="65">
@@ -1066,7 +1066,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2255.7</v>
+        <v>1310.1</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2255.7</v>
+        <v>1310.1</v>
       </c>
     </row>
     <row r="70">
@@ -1114,7 +1114,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2275.3</v>
+        <v>1280.5</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2275.3</v>
+        <v>1280.5</v>
       </c>
     </row>
     <row r="75">
@@ -1162,7 +1162,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1319.9</v>
+        <v>1034.2</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1319.9</v>
+        <v>1034.2</v>
       </c>
     </row>
     <row r="80">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1290.4</v>
+        <v>1004.7</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -1225,108 +1225,12 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1290.4</v>
+        <v>1004.7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Signal:</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>FID1B</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Sample Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>1182</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Sum</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr"/>
-      <c r="B90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Signal:</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>FID1B</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Sample Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>1162.3</v>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Sum</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>1162.3</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr"/>
-      <c r="B95" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src-tauri/samples/mame/16_mame_agilent_numeric_confirmation.xlsx
+++ b/src-tauri/samples/mame/16_mame_agilent_numeric_confirmation.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B85"/>
+  <dimension ref="A1:B115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1232,6 +1232,294 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr"/>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>1398.7</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1398.7</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>1359.3</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1359.3</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1654.8</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1654.8</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1615.4</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1615.4</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>1182</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Signal:</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>FID1B</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Sample Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>1142.6</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1142.6</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
